--- a/data_modelos/3_Indicadores_climáticos.xlsx
+++ b/data_modelos/3_Indicadores_climáticos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\PDE\DEMO\data_modelos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6218E17-9105-4477-B086-5244FC15302F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{651B1004-6D87-4B2F-A31A-36CF319D733F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Corriente" sheetId="10" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1590" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1598" uniqueCount="230">
   <si>
     <t>Lat</t>
   </si>
@@ -733,6 +733,9 @@
   </si>
   <si>
     <t>Lon</t>
+  </si>
+  <si>
+    <t>Número de días al año con precipitación ≥ 20 mm</t>
   </si>
 </sst>
 </file>
@@ -8417,7 +8420,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:U151"/>
+  <dimension ref="A1:U153"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="98.125" bestFit="1" customWidth="1"/>
@@ -17340,6 +17343,124 @@
         <v>215</v>
       </c>
       <c r="S151">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="152" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>229</v>
+      </c>
+      <c r="B152" t="s">
+        <v>229</v>
+      </c>
+      <c r="C152" t="s">
+        <v>1</v>
+      </c>
+      <c r="D152" t="s">
+        <v>2</v>
+      </c>
+      <c r="E152">
+        <v>120</v>
+      </c>
+      <c r="F152">
+        <v>100</v>
+      </c>
+      <c r="G152">
+        <v>152</v>
+      </c>
+      <c r="H152">
+        <v>140</v>
+      </c>
+      <c r="I152">
+        <v>176</v>
+      </c>
+      <c r="J152">
+        <v>164</v>
+      </c>
+      <c r="K152">
+        <v>205</v>
+      </c>
+      <c r="L152">
+        <v>178</v>
+      </c>
+      <c r="M152">
+        <v>238</v>
+      </c>
+      <c r="N152">
+        <v>250</v>
+      </c>
+      <c r="O152">
+        <v>270</v>
+      </c>
+      <c r="P152">
+        <v>202</v>
+      </c>
+      <c r="Q152">
+        <v>305</v>
+      </c>
+      <c r="R152">
+        <v>215</v>
+      </c>
+      <c r="S152">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="153" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>229</v>
+      </c>
+      <c r="B153" t="s">
+        <v>229</v>
+      </c>
+      <c r="C153" t="s">
+        <v>1</v>
+      </c>
+      <c r="D153" t="s">
+        <v>19</v>
+      </c>
+      <c r="E153">
+        <v>120</v>
+      </c>
+      <c r="F153">
+        <v>100</v>
+      </c>
+      <c r="G153">
+        <v>152</v>
+      </c>
+      <c r="H153">
+        <v>140</v>
+      </c>
+      <c r="I153">
+        <v>176</v>
+      </c>
+      <c r="J153">
+        <v>164</v>
+      </c>
+      <c r="K153">
+        <v>205</v>
+      </c>
+      <c r="L153">
+        <v>178</v>
+      </c>
+      <c r="M153">
+        <v>238</v>
+      </c>
+      <c r="N153">
+        <v>250</v>
+      </c>
+      <c r="O153">
+        <v>270</v>
+      </c>
+      <c r="P153">
+        <v>202</v>
+      </c>
+      <c r="Q153">
+        <v>305</v>
+      </c>
+      <c r="R153">
+        <v>215</v>
+      </c>
+      <c r="S153">
         <v>340</v>
       </c>
     </row>

--- a/data_modelos/3_Indicadores_climáticos.xlsx
+++ b/data_modelos/3_Indicadores_climáticos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\PDE\DEMO\data_modelos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{651B1004-6D87-4B2F-A31A-36CF319D733F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CA303E9-961D-4F41-AD1A-23DBB7554850}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
